--- a/spec-tech/ig/StructureDefinition-xdmActorXds.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmActorXds.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:32:10+00:00</t>
+    <t>2026-07-23T16:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmActorXds.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmActorXds.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:03:49+00:00</t>
+    <t>2026-07-23T16:11:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmActorXds.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmActorXds.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:11:23+00:00</t>
+    <t>2026-07-27T13:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
